--- a/exports/Kakawa_Chocolates_Enterprise_SEO_Package_v19/06_QA_and_Manifest/Kakawa_QA_v19.xlsx
+++ b/exports/Kakawa_Chocolates_Enterprise_SEO_Package_v19/06_QA_and_Manifest/Kakawa_QA_v19.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="1" r:id="R1cc38214258e49df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Gates" sheetId="2" r:id="Re7828faa15fd4965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="3" r:id="R35d57e804e0044f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Availability Matrix" sheetId="4" r:id="R60aabb727a624ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generation Ledger" sheetId="5" r:id="R467093f861354b7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="1" r:id="Rc7147d8800364b53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Gates" sheetId="2" r:id="R766274f894344d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="3" r:id="R3d712235aebf4afa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Availability Matrix" sheetId="4" r:id="Rb7d4b153729142f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generation Ledger" sheetId="5" r:id="Rd9f934da75d24fca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -796,7 +796,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re337c44514cc46c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd8a6ee27bda4de1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -906,10 +906,10 @@
         <x:v>Canonical actions</x:v>
       </x:c>
       <x:c r="B8" t="n">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C8" t="n">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" t="str">
         <x:v>PASS</x:v>
@@ -926,10 +926,10 @@
         <x:v>Content assets</x:v>
       </x:c>
       <x:c r="B9" t="n">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" t="n">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" t="str">
         <x:v>PASS</x:v>
@@ -991,7 +991,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf0373c50bc54d29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14b8c4f8cf9a4424"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1231,7 +1231,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c1beb72003b49bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R230533ed80b24207"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1400,7 +1400,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>ef4baae3-4a11-49b2-afd1-d2c93de056de</x:v>
+        <x:v>99d02adb-461c-4794-90b3-f0c4cad7b435</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>Evidence-constrained package strategy synthesis</x:v>
@@ -1418,13 +1418,13 @@
         <x:v>available</x:v>
       </x:c>
       <x:c r="G8" t="str">
-        <x:v>147ad488c696b4e7a11cd1cf73965f639e30d2ce30de78c0e1b50b658c3b9607</x:v>
+        <x:v>898039ad48b7c367882a2f2b9c4d4427fe84a3b47436f1838adc424dc328a83e</x:v>
       </x:c>
       <x:c r="H8" t="str">
-        <x:v>2251043fa6839048072ff74a3d569fd28e6e844d5db6233a2d0d372d1da69bad</x:v>
+        <x:v>0d7d82ea78814d03f6d59d983da99e183f8708a1e34e7210e400361173659e00</x:v>
       </x:c>
       <x:c r="I8" t="n">
-        <x:v>16731</x:v>
+        <x:v>23120</x:v>
       </x:c>
       <x:c r="J8" s="13"/>
       <x:c r="K8" t="str">
@@ -1438,7 +1438,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13cb8fec8f4542ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42fd642cdff14ba7"/>
   </x:tableParts>
 </x:worksheet>
 </file>